--- a/feat/albert-translate/ig/StructureDefinition-cds-fr-related-person.xlsx
+++ b/feat/albert-translate/ig/StructureDefinition-cds-fr-related-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T15:26:57+00:00</t>
+    <t>2026-06-02T15:29:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/albert-translate/ig/StructureDefinition-cds-fr-related-person.xlsx
+++ b/feat/albert-translate/ig/StructureDefinition-cds-fr-related-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T15:29:53+00:00</t>
+    <t>2026-06-02T15:37:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/albert-translate/ig/StructureDefinition-cds-fr-related-person.xlsx
+++ b/feat/albert-translate/ig/StructureDefinition-cds-fr-related-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T15:37:52+00:00</t>
+    <t>2026-06-02T15:42:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/albert-translate/ig/StructureDefinition-cds-fr-related-person.xlsx
+++ b/feat/albert-translate/ig/StructureDefinition-cds-fr-related-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T15:42:18+00:00</t>
+    <t>2026-06-02T15:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/albert-translate/ig/StructureDefinition-cds-fr-related-person.xlsx
+++ b/feat/albert-translate/ig/StructureDefinition-cds-fr-related-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T15:43:30+00:00</t>
+    <t>2026-06-02T16:35:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/albert-translate/ig/StructureDefinition-cds-fr-related-person.xlsx
+++ b/feat/albert-translate/ig/StructureDefinition-cds-fr-related-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T16:35:35+00:00</t>
+    <t>2026-06-02T16:40:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/albert-translate/ig/StructureDefinition-cds-fr-related-person.xlsx
+++ b/feat/albert-translate/ig/StructureDefinition-cds-fr-related-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T16:40:13+00:00</t>
+    <t>2026-06-22T16:37:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
